--- a/测试文件/2320-detail/印花税明细.xlsx
+++ b/测试文件/2320-detail/印花税明细.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\epc-test\测试文件\2320-detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E0AA26-0A3E-4D5D-99DC-E4544B478D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA6D3BC-6E36-4366-9A2A-0213AC6A02CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="1770" windowWidth="21600" windowHeight="12825" xr2:uid="{54836530-C3DE-4C44-95FF-DC577FDEBC19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{54836530-C3DE-4C44-95FF-DC577FDEBC19}"/>
   </bookViews>
   <sheets>
     <sheet name="印花税明细" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="\A">#REF!</definedName>
     <definedName name="DATA1" localSheetId="0">#REF!</definedName>
@@ -70,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>采购合同（取自合同台账-采购合同）</t>
   </si>
@@ -190,6 +187,14 @@
   </si>
   <si>
     <t>总计</t>
+  </si>
+  <si>
+    <t>建设工程合同-工程施工合同</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>建设工程合同-工程设计合同</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -282,47 +287,47 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -340,62 +345,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="累计税金汇总表"/>
-      <sheetName val="累计项目税收明细表202512"/>
-      <sheetName val="累计项目税收明细表2017-202302"/>
-      <sheetName val="增值税表一 累计销项"/>
-      <sheetName val="账税差异监控"/>
-      <sheetName val="12月BS"/>
-      <sheetName val="12月PL"/>
-      <sheetName val="09月CL"/>
-      <sheetName val="收入"/>
-      <sheetName val="销项明细"/>
-      <sheetName val="进项明细"/>
-      <sheetName val="所得税明细"/>
-      <sheetName val="印花税明细"/>
-      <sheetName val="Ref 1_202512_Summary"/>
-      <sheetName val="Ref 2_202512增值税销项 （样式）"/>
-      <sheetName val="Ref 3_202512增值税进项认证清单"/>
-      <sheetName val="Ref 4_202512增值税变动表"/>
-      <sheetName val="预开票收入计提及冲回统计（导入）"/>
-      <sheetName val="未开票数监控"/>
-      <sheetName val="睿景项目累计申报"/>
-      <sheetName val="睿景项目累计缴纳"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -719,587 +668,587 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B3:L37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="18.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="12.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="16.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
-    <col min="11" max="12" width="30.375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="18.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="16.58203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="30.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C4" s="4" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>-6649253.4977358496</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>-1994.78</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6">
+      <c r="D6" s="4"/>
+      <c r="E6" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>461162.19</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>461.16</v>
       </c>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
+      <c r="D8" s="4"/>
+      <c r="E8" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>590070255.53699994</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>177021.08</v>
       </c>
     </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6">
+      <c r="D10" s="4"/>
+      <c r="E10" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C11" s="4" t="s">
+    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>3872941123.0900002</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>1161882.3400000001</v>
       </c>
     </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6">
+      <c r="D12" s="4"/>
+      <c r="E12" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C13" s="4" t="s">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>400540.81</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>120.16</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>4457223828.1292601</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5">
+      <c r="E14" s="3"/>
+      <c r="F14" s="4">
         <v>1337489.96</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="F15" s="3"/>
-      <c r="J15" s="7" t="s">
+    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="F15" s="2"/>
+      <c r="J15" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="F16" s="3"/>
-      <c r="J16" s="7" t="s">
+    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="F16" s="2"/>
+      <c r="J16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="F17" s="3"/>
-      <c r="J17" s="7" t="s">
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F17" s="2"/>
+      <c r="J17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="9" t="s">
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="J18" s="7" t="s">
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="J18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="7">
         <v>400540.81</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="7">
         <v>120.16</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C19" s="4" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="9">
         <v>202511</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="9">
         <v>202510</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C20" s="4" t="s">
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="10">
         <v>4632631431.1643696</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="8">
         <v>1389789.43</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <v>1636122166.6199999</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="2">
         <v>50555057.539999999</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="4" t="s">
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <v>969150103.38</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="8">
         <v>290745.03000000003</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="2">
         <v>125907666.86</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="2">
         <v>53264485.479999997</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C22" s="4" t="s">
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="10">
         <v>169354129.27620301</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="8">
         <v>50806.239999999998</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <v>-22711643.440000001</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="2">
         <v>13275081.42</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C23" s="4" t="s">
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="10">
         <v>5771135663.82057</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="10">
+      <c r="E23" s="3"/>
+      <c r="F23" s="8">
         <v>1731340.7</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <v>1739318190.04</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="2">
         <v>117094624.44</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <v>590070255.53699994</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="7">
         <v>177021.15</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="D24" s="13"/>
-      <c r="H24" s="3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D24" s="11"/>
+      <c r="H24" s="2">
         <v>1739318190.04</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="2">
         <v>117094624.44</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J25" s="7" t="s">
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="J25" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>-6649253.4977358496</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="7">
         <v>-1994.8</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="14" t="s">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="7">
         <v>3872941123.0900002</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="7">
         <v>1161882.3899999999</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C27" s="4" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>461162.19</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>461.16</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C28" s="4" t="s">
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>0</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="4">
         <v>1559220358.9170001</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>467766.11</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="4">
         <v>162704875.778467</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>48811.46</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C31" s="4" t="s">
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C31" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>8505572554.2543697</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <v>2551671.77</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C32" s="4" t="s">
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>0</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>1E-3</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C33" s="4" t="s">
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>400540.81</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>120.16</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="D34" s="8">
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D34" s="7">
         <v>10228359491.9498</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="7">
         <v>3068830.66</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="D35" s="3">
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D35" s="2">
         <v>10228359491.9498</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>3068830.66</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="7">
         <v>461162.19</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="7">
         <v>461.21</v>
       </c>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="J36" s="7" t="s">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="7">
         <v>-56603.77</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="7">
         <v>-16.98</v>
       </c>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="J37" s="7" t="s">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="7">
         <v>4457167224.3592596</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="7">
         <v>1337473.1299999999</v>
       </c>
     </row>
